--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,2462 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125300204</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>588968</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6931778</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125298949</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6931676</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125294978</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6931823</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125295434</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589353</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6931796</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125300846</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589033</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6931798</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125305277</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589383</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6931790</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125298269</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589340</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6931710</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125294611</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589420</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6931807</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125295350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589353</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6931796</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125299044</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589157</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6931653</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125296528</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589358</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6931874</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125296431</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79919</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589354</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6931848</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125298647</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589287</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6931646</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125299553</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589043</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6931742</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125294642</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589418</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6931797</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125301135</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kångeråbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589154</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6931760</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125300799</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>589008</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6931783</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125299895</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>588936</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6931778</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125294462</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>589418</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6931797</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125299331</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>589048</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6931702</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125296103</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>589391</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6931808</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125300204</v>
+        <v>125294462</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,39 +819,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588968</v>
+        <v>589418</v>
       </c>
       <c r="R3" t="n">
-        <v>6931778</v>
+        <v>6931797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,22 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125298949</v>
+        <v>125300846</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,34 +931,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589168</v>
+        <v>589033</v>
       </c>
       <c r="R4" t="n">
-        <v>6931676</v>
+        <v>6931798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125294978</v>
+        <v>125296431</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,25 +1049,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589387</v>
+        <v>589354</v>
       </c>
       <c r="R5" t="n">
-        <v>6931823</v>
+        <v>6931848</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125295434</v>
+        <v>125300799</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,34 +1165,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589353</v>
+        <v>589008</v>
       </c>
       <c r="R6" t="n">
-        <v>6931796</v>
+        <v>6931783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1239,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,22 +1259,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125300846</v>
+        <v>125294642</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,39 +1287,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589033</v>
+        <v>589418</v>
       </c>
       <c r="R7" t="n">
-        <v>6931798</v>
+        <v>6931797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,12 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,19 +1371,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125305277</v>
+        <v>125296103</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1416,41 +1416,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589383</v>
+        <v>589391</v>
       </c>
       <c r="R8" t="n">
-        <v>6931790</v>
+        <v>6931808</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,14 +1461,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125298269</v>
+        <v>125299331</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,38 +1517,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589340</v>
+        <v>589048</v>
       </c>
       <c r="R9" t="n">
-        <v>6931710</v>
+        <v>6931702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1738,7 +1729,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125295350</v>
+        <v>125298647</v>
       </c>
       <c r="B11" t="n">
         <v>57529</v>
@@ -1779,14 +1770,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589353</v>
+        <v>589287</v>
       </c>
       <c r="R11" t="n">
-        <v>6931796</v>
+        <v>6931646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125299044</v>
+        <v>125295434</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,39 +1862,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589157</v>
+        <v>589353</v>
       </c>
       <c r="R12" t="n">
-        <v>6931653</v>
+        <v>6931796</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,22 +1946,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296528</v>
+        <v>125299895</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,25 +1970,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,14 +1999,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589358</v>
+        <v>588936</v>
       </c>
       <c r="R13" t="n">
-        <v>6931874</v>
+        <v>6931778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,12 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fjäder ( dun )</t>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,22 +2068,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296431</v>
+        <v>125296528</v>
       </c>
       <c r="B14" t="n">
-        <v>79919</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,34 +2096,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589354</v>
+        <v>589358</v>
       </c>
       <c r="R14" t="n">
-        <v>6931848</v>
+        <v>6931874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2179,7 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125298647</v>
+        <v>125298269</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,43 +2214,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589287</v>
+        <v>589340</v>
       </c>
       <c r="R15" t="n">
-        <v>6931646</v>
+        <v>6931710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294642</v>
+        <v>125305277</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,34 +2442,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589418</v>
+        <v>589383</v>
       </c>
       <c r="R17" t="n">
-        <v>6931797</v>
+        <v>6931790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,19 +2523,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:06</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125300799</v>
+        <v>125294978</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,39 +2695,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589008</v>
+        <v>589387</v>
       </c>
       <c r="R19" t="n">
-        <v>6931783</v>
+        <v>6931823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2759,12 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,22 +2779,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125299895</v>
+        <v>125298949</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2807,39 +2807,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588936</v>
+        <v>589168</v>
       </c>
       <c r="R20" t="n">
-        <v>6931778</v>
+        <v>6931676</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2881,12 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125294462</v>
+        <v>125300204</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,34 +2919,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589418</v>
+        <v>588968</v>
       </c>
       <c r="R21" t="n">
-        <v>6931797</v>
+        <v>6931778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,7 +2983,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2998,7 +2993,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,22 +3013,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299331</v>
+        <v>125295350</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3041,34 +3041,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589048</v>
+        <v>589353</v>
       </c>
       <c r="R22" t="n">
-        <v>6931702</v>
+        <v>6931796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,7 +3105,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3110,7 +3115,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,22 +3130,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125296103</v>
+        <v>125299044</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3153,16 +3158,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3173,19 +3178,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589391</v>
+        <v>589157</v>
       </c>
       <c r="R23" t="n">
-        <v>6931808</v>
+        <v>6931653</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,12 +3232,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,12 +3247,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125300846</v>
+        <v>125295434</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +931,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589033</v>
+        <v>589353</v>
       </c>
       <c r="R4" t="n">
-        <v>6931798</v>
+        <v>6931796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,22 +1015,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296431</v>
+        <v>125299895</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1039,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589354</v>
+        <v>588936</v>
       </c>
       <c r="R5" t="n">
-        <v>6931848</v>
+        <v>6931778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,22 +1137,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125300799</v>
+        <v>125298269</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,43 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589008</v>
+        <v>589340</v>
       </c>
       <c r="R6" t="n">
-        <v>6931783</v>
+        <v>6931710</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,12 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125294642</v>
+        <v>125299331</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,34 +1277,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589418</v>
+        <v>589048</v>
       </c>
       <c r="R7" t="n">
-        <v>6931797</v>
+        <v>6931702</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,22 +1361,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125296103</v>
+        <v>125294611</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,39 +1389,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589391</v>
+        <v>589420</v>
       </c>
       <c r="R8" t="n">
-        <v>6931808</v>
+        <v>6931807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,7 +1448,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,12 +1458,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125299331</v>
+        <v>125298949</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,34 +1501,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589048</v>
+        <v>589168</v>
       </c>
       <c r="R9" t="n">
-        <v>6931702</v>
+        <v>6931676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125294611</v>
+        <v>125294978</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,21 +1613,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1657,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589420</v>
+        <v>589387</v>
       </c>
       <c r="R10" t="n">
-        <v>6931807</v>
+        <v>6931823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125298647</v>
+        <v>125296103</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,16 +1725,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1770,14 +1750,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589287</v>
+        <v>589391</v>
       </c>
       <c r="R11" t="n">
-        <v>6931646</v>
+        <v>6931808</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1799,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1819,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125295434</v>
+        <v>125299553</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,38 +1843,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589353</v>
+        <v>589043</v>
       </c>
       <c r="R12" t="n">
-        <v>6931796</v>
+        <v>6931742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,22 +1931,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299895</v>
+        <v>125296528</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,25 +1955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,14 +1984,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588936</v>
+        <v>589358</v>
       </c>
       <c r="R13" t="n">
-        <v>6931778</v>
+        <v>6931874</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2033,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,22 +2053,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296528</v>
+        <v>125300846</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,25 +2077,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,14 +2106,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589358</v>
+        <v>589033</v>
       </c>
       <c r="R14" t="n">
-        <v>6931874</v>
+        <v>6931798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2155,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Fjäder ( dun )</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,22 +2175,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125298269</v>
+        <v>125301135</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,38 +2199,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589340</v>
+        <v>589154</v>
       </c>
       <c r="R15" t="n">
-        <v>6931710</v>
+        <v>6931760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125299553</v>
+        <v>125294642</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,38 +2321,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589043</v>
+        <v>589418</v>
       </c>
       <c r="R16" t="n">
-        <v>6931742</v>
+        <v>6931797</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,22 +2409,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125305277</v>
+        <v>125299044</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,16 +2437,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2459,41 +2454,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589383</v>
+        <v>589157</v>
       </c>
       <c r="R17" t="n">
-        <v>6931790</v>
+        <v>6931653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,14 +2499,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,19 +2526,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125301135</v>
+        <v>125300799</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2598,14 +2579,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589154</v>
+        <v>589008</v>
       </c>
       <c r="R18" t="n">
-        <v>6931760</v>
+        <v>6931783</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2618,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2679,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125294978</v>
+        <v>125300204</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,34 +2676,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589387</v>
+        <v>588968</v>
       </c>
       <c r="R19" t="n">
-        <v>6931823</v>
+        <v>6931778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2740,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2750,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,22 +2770,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125298949</v>
+        <v>125298647</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2807,34 +2798,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589168</v>
+        <v>589287</v>
       </c>
       <c r="R20" t="n">
-        <v>6931676</v>
+        <v>6931646</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2862,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,7 +2899,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125300204</v>
+        <v>125305277</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2936,22 +2932,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588968</v>
+        <v>589383</v>
       </c>
       <c r="R21" t="n">
-        <v>6931778</v>
+        <v>6931790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2981,24 +2996,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,12 +3018,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3142,10 +3147,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125299044</v>
+        <v>125296431</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>79919</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3154,43 +3159,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589157</v>
+        <v>589354</v>
       </c>
       <c r="R23" t="n">
-        <v>6931653</v>
+        <v>6931848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,12 +3247,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125294462</v>
+        <v>125298269</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,38 +815,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589418</v>
+        <v>589340</v>
       </c>
       <c r="R3" t="n">
-        <v>6931797</v>
+        <v>6931710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,22 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125295434</v>
+        <v>125296528</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,38 +927,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589353</v>
+        <v>589358</v>
       </c>
       <c r="R4" t="n">
-        <v>6931796</v>
+        <v>6931874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299895</v>
+        <v>125295350</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,16 +1053,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,14 +1078,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588936</v>
+        <v>589353</v>
       </c>
       <c r="R5" t="n">
-        <v>6931778</v>
+        <v>6931796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,22 +1142,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125298269</v>
+        <v>125299331</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589340</v>
+        <v>589048</v>
       </c>
       <c r="R6" t="n">
-        <v>6931710</v>
+        <v>6931702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299331</v>
+        <v>125299553</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589048</v>
+        <v>589043</v>
       </c>
       <c r="R7" t="n">
-        <v>6931702</v>
+        <v>6931742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125294611</v>
+        <v>125300799</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,34 +1394,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589420</v>
+        <v>589008</v>
       </c>
       <c r="R8" t="n">
-        <v>6931807</v>
+        <v>6931783</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1458,7 +1468,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,22 +1488,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125298949</v>
+        <v>125294978</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,34 +1516,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589168</v>
+        <v>589387</v>
       </c>
       <c r="R9" t="n">
-        <v>6931676</v>
+        <v>6931823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,19 +1600,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125294978</v>
+        <v>125295434</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1637,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589387</v>
+        <v>589353</v>
       </c>
       <c r="R10" t="n">
-        <v>6931823</v>
+        <v>6931796</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,7 +1724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125296103</v>
+        <v>125300204</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1750,14 +1765,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589391</v>
+        <v>588968</v>
       </c>
       <c r="R11" t="n">
-        <v>6931808</v>
+        <v>6931778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,12 +1814,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125299553</v>
+        <v>125298647</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,38 +1858,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589043</v>
+        <v>589287</v>
       </c>
       <c r="R12" t="n">
-        <v>6931742</v>
+        <v>6931646</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296528</v>
+        <v>125296431</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,39 +1979,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589358</v>
+        <v>589354</v>
       </c>
       <c r="R13" t="n">
-        <v>6931874</v>
+        <v>6931848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,12 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125300846</v>
+        <v>125294462</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,39 +2091,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589033</v>
+        <v>589418</v>
       </c>
       <c r="R14" t="n">
-        <v>6931798</v>
+        <v>6931797</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,12 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,19 +2175,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125301135</v>
+        <v>125296103</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589154</v>
+        <v>589391</v>
       </c>
       <c r="R15" t="n">
-        <v>6931760</v>
+        <v>6931808</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,22 +2297,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125294642</v>
+        <v>125299044</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,34 +2325,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589418</v>
+        <v>589157</v>
       </c>
       <c r="R16" t="n">
-        <v>6931797</v>
+        <v>6931653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2399,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,22 +2414,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125299044</v>
+        <v>125294611</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,39 +2442,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589157</v>
+        <v>589420</v>
       </c>
       <c r="R17" t="n">
-        <v>6931653</v>
+        <v>6931807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,19 +2526,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125300799</v>
+        <v>125299895</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589008</v>
+        <v>588936</v>
       </c>
       <c r="R18" t="n">
-        <v>6931783</v>
+        <v>6931778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,7 +2660,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125300204</v>
+        <v>125305277</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2693,22 +2693,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588968</v>
+        <v>589383</v>
       </c>
       <c r="R19" t="n">
-        <v>6931778</v>
+        <v>6931790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,24 +2757,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,22 +2779,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125298647</v>
+        <v>125301135</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,16 +2807,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2827,10 +2836,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589287</v>
+        <v>589154</v>
       </c>
       <c r="R20" t="n">
-        <v>6931646</v>
+        <v>6931760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2862,7 +2871,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2872,7 +2881,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125305277</v>
+        <v>125298949</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,58 +2929,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589383</v>
+        <v>589168</v>
       </c>
       <c r="R21" t="n">
-        <v>6931790</v>
+        <v>6931676</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2996,14 +2986,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3018,22 +3013,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125295350</v>
+        <v>125294642</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3046,39 +3041,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589353</v>
+        <v>589418</v>
       </c>
       <c r="R22" t="n">
-        <v>6931796</v>
+        <v>6931797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3110,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3120,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125296431</v>
+        <v>125300846</v>
       </c>
       <c r="B23" t="n">
-        <v>79919</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3159,38 +3149,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589354</v>
+        <v>589033</v>
       </c>
       <c r="R23" t="n">
-        <v>6931848</v>
+        <v>6931798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,7 +3227,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,12 +3247,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125295350</v>
+        <v>125299331</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,39 +1053,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589353</v>
+        <v>589048</v>
       </c>
       <c r="R5" t="n">
-        <v>6931796</v>
+        <v>6931702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,22 +1137,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125299331</v>
+        <v>125295350</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,34 +1165,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589048</v>
+        <v>589353</v>
       </c>
       <c r="R6" t="n">
-        <v>6931702</v>
+        <v>6931796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125300204</v>
+        <v>125298647</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588968</v>
+        <v>589287</v>
       </c>
       <c r="R11" t="n">
-        <v>6931778</v>
+        <v>6931646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,12 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125298647</v>
+        <v>125300204</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,16 +1857,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1887,14 +1882,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589287</v>
+        <v>588968</v>
       </c>
       <c r="R12" t="n">
-        <v>6931646</v>
+        <v>6931778</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2538,7 +2538,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125299895</v>
+        <v>125305277</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2571,22 +2571,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588936</v>
+        <v>589383</v>
       </c>
       <c r="R18" t="n">
-        <v>6931778</v>
+        <v>6931790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,24 +2635,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,19 +2657,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125305277</v>
+        <v>125299895</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2693,41 +2702,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589383</v>
+        <v>588936</v>
       </c>
       <c r="R19" t="n">
-        <v>6931790</v>
+        <v>6931778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,14 +2747,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,12 +2779,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125298269</v>
+        <v>125299044</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,38 +815,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589340</v>
+        <v>589157</v>
       </c>
       <c r="R3" t="n">
-        <v>6931710</v>
+        <v>6931653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296528</v>
+        <v>125296431</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589358</v>
+        <v>589354</v>
       </c>
       <c r="R4" t="n">
-        <v>6931874</v>
+        <v>6931848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299331</v>
+        <v>125298647</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,34 +1048,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589048</v>
+        <v>589287</v>
       </c>
       <c r="R5" t="n">
-        <v>6931702</v>
+        <v>6931646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125295350</v>
+        <v>125300846</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589353</v>
+        <v>589033</v>
       </c>
       <c r="R6" t="n">
-        <v>6931796</v>
+        <v>6931798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,22 +1259,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299553</v>
+        <v>125294462</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,38 +1283,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589043</v>
+        <v>589418</v>
       </c>
       <c r="R7" t="n">
-        <v>6931742</v>
+        <v>6931797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,12 +1371,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1612,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125295434</v>
+        <v>125298949</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,34 +1633,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589353</v>
+        <v>589168</v>
       </c>
       <c r="R10" t="n">
-        <v>6931796</v>
+        <v>6931676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,22 +1717,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125298647</v>
+        <v>125294642</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,39 +1745,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589287</v>
+        <v>589418</v>
       </c>
       <c r="R11" t="n">
-        <v>6931646</v>
+        <v>6931797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,19 +1829,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125300204</v>
+        <v>125299895</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588968</v>
+        <v>588936</v>
       </c>
       <c r="R12" t="n">
         <v>6931778</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125296431</v>
+        <v>125299331</v>
       </c>
       <c r="B13" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589354</v>
+        <v>589048</v>
       </c>
       <c r="R13" t="n">
-        <v>6931848</v>
+        <v>6931702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,22 +2063,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125294462</v>
+        <v>125296103</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,34 +2091,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589418</v>
+        <v>589391</v>
       </c>
       <c r="R14" t="n">
-        <v>6931797</v>
+        <v>6931808</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,7 +2197,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125296103</v>
+        <v>125305277</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2220,22 +2230,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589391</v>
+        <v>589383</v>
       </c>
       <c r="R15" t="n">
-        <v>6931808</v>
+        <v>6931790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,24 +2294,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125299044</v>
+        <v>125294611</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,39 +2344,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589157</v>
+        <v>589420</v>
       </c>
       <c r="R16" t="n">
-        <v>6931653</v>
+        <v>6931807</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,7 +2403,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,7 +2413,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,22 +2428,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294611</v>
+        <v>125296528</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,38 +2452,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589420</v>
+        <v>589358</v>
       </c>
       <c r="R17" t="n">
-        <v>6931807</v>
+        <v>6931874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2530,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,7 +2562,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125305277</v>
+        <v>125300204</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2571,41 +2595,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589383</v>
+        <v>588968</v>
       </c>
       <c r="R18" t="n">
-        <v>6931790</v>
+        <v>6931778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2635,14 +2640,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,22 +2672,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125299895</v>
+        <v>125298269</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,43 +2696,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588936</v>
+        <v>589340</v>
       </c>
       <c r="R19" t="n">
-        <v>6931778</v>
+        <v>6931710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,7 +2759,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2759,12 +2769,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2796,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125301135</v>
+        <v>125295434</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2807,39 +2812,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589154</v>
+        <v>589353</v>
       </c>
       <c r="R20" t="n">
-        <v>6931760</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2881,12 +2881,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,22 +2896,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125298949</v>
+        <v>125295350</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,34 +2924,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589168</v>
+        <v>589353</v>
       </c>
       <c r="R21" t="n">
-        <v>6931676</v>
+        <v>6931796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,22 +3013,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294642</v>
+        <v>125299553</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,38 +3037,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589418</v>
+        <v>589043</v>
       </c>
       <c r="R22" t="n">
-        <v>6931797</v>
+        <v>6931742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,19 +3125,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125300846</v>
+        <v>125301135</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589033</v>
+        <v>589154</v>
       </c>
       <c r="R23" t="n">
-        <v>6931798</v>
+        <v>6931760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124845031</v>
       </c>
       <c r="B2" t="n">
-        <v>56821</v>
+        <v>56939</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299044</v>
+        <v>125296528</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,43 +815,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589157</v>
+        <v>589358</v>
       </c>
       <c r="R3" t="n">
-        <v>6931653</v>
+        <v>6931874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,22 +913,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125296431</v>
+        <v>125299553</v>
       </c>
       <c r="B4" t="n">
-        <v>79919</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,34 +941,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589354</v>
+        <v>589043</v>
       </c>
       <c r="R4" t="n">
-        <v>6931848</v>
+        <v>6931742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,22 +1025,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125298647</v>
+        <v>125299895</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,16 +1053,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,14 +1078,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589287</v>
+        <v>588936</v>
       </c>
       <c r="R5" t="n">
-        <v>6931646</v>
+        <v>6931778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1127,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125300846</v>
+        <v>125305277</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,22 +1192,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589033</v>
+        <v>589383</v>
       </c>
       <c r="R6" t="n">
-        <v>6931798</v>
+        <v>6931790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,24 +1256,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,22 +1278,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125294462</v>
+        <v>125294611</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589418</v>
+        <v>589420</v>
       </c>
       <c r="R7" t="n">
-        <v>6931797</v>
+        <v>6931807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125300799</v>
+        <v>125298949</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,39 +1418,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589008</v>
+        <v>589168</v>
       </c>
       <c r="R8" t="n">
-        <v>6931783</v>
+        <v>6931676</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,12 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125294978</v>
+        <v>125300204</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,34 +1530,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589387</v>
+        <v>588968</v>
       </c>
       <c r="R9" t="n">
-        <v>6931823</v>
+        <v>6931778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,22 +1624,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125298949</v>
+        <v>125300846</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,34 +1652,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589168</v>
+        <v>589033</v>
       </c>
       <c r="R10" t="n">
-        <v>6931676</v>
+        <v>6931798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1726,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125294642</v>
+        <v>125296431</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>80056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,25 +1770,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589418</v>
+        <v>589354</v>
       </c>
       <c r="R11" t="n">
-        <v>6931797</v>
+        <v>6931848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125299895</v>
+        <v>125294978</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,39 +1886,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588936</v>
+        <v>589387</v>
       </c>
       <c r="R12" t="n">
-        <v>6931778</v>
+        <v>6931823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,22 +1970,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299331</v>
+        <v>125294642</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,34 +1998,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589048</v>
+        <v>589418</v>
       </c>
       <c r="R13" t="n">
-        <v>6931702</v>
+        <v>6931797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,22 +2082,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125296103</v>
+        <v>125299044</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,16 +2110,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2111,19 +2130,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589391</v>
+        <v>589157</v>
       </c>
       <c r="R14" t="n">
-        <v>6931808</v>
+        <v>6931653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,22 +2199,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125305277</v>
+        <v>125298647</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,16 +2227,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2230,41 +2244,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589383</v>
+        <v>589287</v>
       </c>
       <c r="R15" t="n">
-        <v>6931790</v>
+        <v>6931646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,14 +2289,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,22 +2316,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125294611</v>
+        <v>125301135</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,34 +2344,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589420</v>
+        <v>589154</v>
       </c>
       <c r="R16" t="n">
-        <v>6931807</v>
+        <v>6931760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,7 +2418,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,22 +2438,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125296528</v>
+        <v>125294462</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,43 +2462,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589358</v>
+        <v>589418</v>
       </c>
       <c r="R17" t="n">
-        <v>6931874</v>
+        <v>6931797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,12 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125300204</v>
+        <v>125299331</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,39 +2578,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588968</v>
+        <v>589048</v>
       </c>
       <c r="R18" t="n">
-        <v>6931778</v>
+        <v>6931702</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,12 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125298269</v>
+        <v>125295350</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>57632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2696,38 +2686,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589340</v>
+        <v>589353</v>
       </c>
       <c r="R19" t="n">
-        <v>6931710</v>
+        <v>6931796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2769,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,22 +2779,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125295434</v>
+        <v>125298269</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>97147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2808,38 +2803,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589353</v>
+        <v>589340</v>
       </c>
       <c r="R20" t="n">
-        <v>6931796</v>
+        <v>6931710</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2881,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,22 +2891,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125295350</v>
+        <v>125300799</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,16 +2919,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2949,14 +2944,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589353</v>
+        <v>589008</v>
       </c>
       <c r="R21" t="n">
-        <v>6931796</v>
+        <v>6931783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,7 +2983,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2998,7 +2993,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,22 +3013,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125299553</v>
+        <v>125295434</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,38 +3037,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589043</v>
+        <v>589353</v>
       </c>
       <c r="R22" t="n">
-        <v>6931742</v>
+        <v>6931796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,22 +3125,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125301135</v>
+        <v>125296103</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589154</v>
+        <v>589391</v>
       </c>
       <c r="R23" t="n">
-        <v>6931760</v>
+        <v>6931808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,12 +3247,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125299553</v>
+        <v>125305277</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589043</v>
+        <v>589383</v>
       </c>
       <c r="R4" t="n">
-        <v>6931742</v>
+        <v>6931790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +1022,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:56</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,22 +1044,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299895</v>
+        <v>125294611</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,39 +1072,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588936</v>
+        <v>589420</v>
       </c>
       <c r="R5" t="n">
-        <v>6931778</v>
+        <v>6931807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,12 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,22 +1156,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125305277</v>
+        <v>125299553</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>100451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,62 +1180,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589383</v>
+        <v>589043</v>
       </c>
       <c r="R6" t="n">
-        <v>6931790</v>
+        <v>6931742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,14 +1241,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,22 +1268,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125294611</v>
+        <v>125299895</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,34 +1296,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589420</v>
+        <v>588936</v>
       </c>
       <c r="R7" t="n">
-        <v>6931807</v>
+        <v>6931778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,12 +1390,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125296528</v>
+        <v>125299044</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
+        <v>56828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,43 +815,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589358</v>
+        <v>589157</v>
       </c>
       <c r="R3" t="n">
-        <v>6931874</v>
+        <v>6931653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,22 +908,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125305277</v>
+        <v>125295350</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,41 +953,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589383</v>
+        <v>589353</v>
       </c>
       <c r="R4" t="n">
-        <v>6931790</v>
+        <v>6931796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,14 +998,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125294611</v>
+        <v>125300204</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,34 +1053,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589420</v>
+        <v>588968</v>
       </c>
       <c r="R5" t="n">
-        <v>6931807</v>
+        <v>6931778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1127,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,22 +1147,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125299553</v>
+        <v>125305277</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,38 +1171,62 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589043</v>
+        <v>589383</v>
       </c>
       <c r="R6" t="n">
-        <v>6931742</v>
+        <v>6931790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,19 +1256,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:56</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,22 +1278,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299895</v>
+        <v>125294462</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,39 +1306,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588936</v>
+        <v>589418</v>
       </c>
       <c r="R7" t="n">
-        <v>6931778</v>
+        <v>6931797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,22 +1390,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125298949</v>
+        <v>125299895</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,34 +1418,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589168</v>
+        <v>588936</v>
       </c>
       <c r="R8" t="n">
-        <v>6931676</v>
+        <v>6931778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1492,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125300204</v>
+        <v>125294642</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,39 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588968</v>
+        <v>589418</v>
       </c>
       <c r="R9" t="n">
-        <v>6931778</v>
+        <v>6931797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,22 +1624,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125300846</v>
+        <v>125298269</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,43 +1648,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589033</v>
+        <v>589340</v>
       </c>
       <c r="R10" t="n">
-        <v>6931798</v>
+        <v>6931710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,12 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125296431</v>
+        <v>125300846</v>
       </c>
       <c r="B11" t="n">
-        <v>80056</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,38 +1760,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589354</v>
+        <v>589033</v>
       </c>
       <c r="R11" t="n">
-        <v>6931848</v>
+        <v>6931798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,22 +1858,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125294978</v>
+        <v>125298949</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,34 +1886,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589387</v>
+        <v>589168</v>
       </c>
       <c r="R12" t="n">
-        <v>6931823</v>
+        <v>6931676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,22 +1970,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125294642</v>
+        <v>125301135</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1998,34 +1998,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589418</v>
+        <v>589154</v>
       </c>
       <c r="R13" t="n">
-        <v>6931797</v>
+        <v>6931760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2062,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +2072,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,22 +2092,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125299044</v>
+        <v>125298647</v>
       </c>
       <c r="B14" t="n">
-        <v>56828</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,16 +2120,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2130,7 +2140,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2139,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589157</v>
+        <v>589287</v>
       </c>
       <c r="R14" t="n">
-        <v>6931653</v>
+        <v>6931646</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2184,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2194,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,10 +2221,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125298647</v>
+        <v>125299553</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
+        <v>100451</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,43 +2233,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589287</v>
+        <v>589043</v>
       </c>
       <c r="R15" t="n">
-        <v>6931646</v>
+        <v>6931742</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2306,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125301135</v>
+        <v>125295434</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,39 +2349,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589154</v>
+        <v>589353</v>
       </c>
       <c r="R16" t="n">
-        <v>6931760</v>
+        <v>6931796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,12 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,22 +2433,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294462</v>
+        <v>125294611</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2466,21 +2461,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2490,10 +2485,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589418</v>
+        <v>589420</v>
       </c>
       <c r="R17" t="n">
-        <v>6931797</v>
+        <v>6931807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125299331</v>
+        <v>125296431</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>80056</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,38 +2569,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589048</v>
+        <v>589354</v>
       </c>
       <c r="R18" t="n">
-        <v>6931702</v>
+        <v>6931848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2642,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,22 +2657,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125295350</v>
+        <v>125299331</v>
       </c>
       <c r="B19" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,39 +2685,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589353</v>
+        <v>589048</v>
       </c>
       <c r="R19" t="n">
-        <v>6931796</v>
+        <v>6931702</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2744,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2754,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,22 +2769,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125298269</v>
+        <v>125296103</v>
       </c>
       <c r="B20" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,38 +2793,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589340</v>
+        <v>589391</v>
       </c>
       <c r="R20" t="n">
-        <v>6931710</v>
+        <v>6931808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2871,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,22 +2891,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125300799</v>
+        <v>125294978</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2919,39 +2919,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589008</v>
+        <v>589387</v>
       </c>
       <c r="R21" t="n">
-        <v>6931783</v>
+        <v>6931823</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,7 +2978,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2993,12 +2988,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,22 +3003,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125295434</v>
+        <v>125296528</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,38 +3027,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589353</v>
+        <v>589358</v>
       </c>
       <c r="R22" t="n">
-        <v>6931796</v>
+        <v>6931874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,7 +3095,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3110,7 +3105,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,7 +3137,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125296103</v>
+        <v>125300799</v>
       </c>
       <c r="B23" t="n">
         <v>57635</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589391</v>
+        <v>589008</v>
       </c>
       <c r="R23" t="n">
-        <v>6931808</v>
+        <v>6931783</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,12 +3247,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299044</v>
+        <v>125295350</v>
       </c>
       <c r="B3" t="n">
-        <v>56828</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,19 +839,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589157</v>
+        <v>589353</v>
       </c>
       <c r="R3" t="n">
-        <v>6931653</v>
+        <v>6931796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,22 +908,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125295350</v>
+        <v>125299044</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>56828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,19 +956,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589353</v>
+        <v>589157</v>
       </c>
       <c r="R4" t="n">
-        <v>6931796</v>
+        <v>6931653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,12 +1025,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125298269</v>
+        <v>125300846</v>
       </c>
       <c r="B10" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,38 +1648,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589340</v>
+        <v>589033</v>
       </c>
       <c r="R10" t="n">
-        <v>6931710</v>
+        <v>6931798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1726,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125300846</v>
+        <v>125298269</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,43 +1770,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589033</v>
+        <v>589340</v>
       </c>
       <c r="R11" t="n">
-        <v>6931798</v>
+        <v>6931710</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>56939</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>
@@ -803,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125295350</v>
+        <v>125300799</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -844,14 +834,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589353</v>
+        <v>589008</v>
       </c>
       <c r="R3" t="n">
-        <v>6931796</v>
+        <v>6931783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,27 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125299044</v>
+        <v>125294642</v>
       </c>
       <c r="B4" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,39 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589157</v>
+        <v>589418</v>
       </c>
       <c r="R4" t="n">
-        <v>6931653</v>
+        <v>6931797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,49 +1010,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125300204</v>
+        <v>125296528</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,14 +1058,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588968</v>
+        <v>589358</v>
       </c>
       <c r="R5" t="n">
-        <v>6931778</v>
+        <v>6931874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,27 +1127,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125305277</v>
+        <v>125296103</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,41 +1167,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589383</v>
+        <v>589391</v>
       </c>
       <c r="R6" t="n">
-        <v>6931790</v>
+        <v>6931808</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,14 +1212,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,15 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125294462</v>
+        <v>125300846</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,34 +1267,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589418</v>
+        <v>589033</v>
       </c>
       <c r="R7" t="n">
-        <v>6931797</v>
+        <v>6931798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,27 +1361,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125299895</v>
+        <v>125294611</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,39 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588936</v>
+        <v>589420</v>
       </c>
       <c r="R8" t="n">
-        <v>6931778</v>
+        <v>6931807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,12 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,27 +1468,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125294642</v>
+        <v>125300204</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,34 +1491,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589418</v>
+        <v>588968</v>
       </c>
       <c r="R9" t="n">
-        <v>6931797</v>
+        <v>6931778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1565,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,27 +1585,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125300846</v>
+        <v>125294978</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,39 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589033</v>
+        <v>589387</v>
       </c>
       <c r="R10" t="n">
-        <v>6931798</v>
+        <v>6931823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,12 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,62 +1692,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125298269</v>
+        <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589340</v>
+        <v>589353</v>
       </c>
       <c r="R11" t="n">
-        <v>6931710</v>
+        <v>6931796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,62 +1804,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125298949</v>
+        <v>125299553</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589168</v>
+        <v>589043</v>
       </c>
       <c r="R12" t="n">
-        <v>6931676</v>
+        <v>6931742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,12 +1926,7 @@
         <v>125301135</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,15 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125298647</v>
+        <v>125299331</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,39 +2051,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589287</v>
+        <v>589048</v>
       </c>
       <c r="R14" t="n">
-        <v>6931646</v>
+        <v>6931702</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,7 +2120,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,50 +2147,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125299553</v>
+        <v>125299044</v>
       </c>
       <c r="B15" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589043</v>
+        <v>589157</v>
       </c>
       <c r="R15" t="n">
-        <v>6931742</v>
+        <v>6931653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,15 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125295434</v>
+        <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,34 +2270,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589353</v>
+        <v>589287</v>
       </c>
       <c r="R16" t="n">
-        <v>6931796</v>
+        <v>6931646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,62 +2359,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294611</v>
+        <v>125298269</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589420</v>
+        <v>589340</v>
       </c>
       <c r="R17" t="n">
-        <v>6931807</v>
+        <v>6931710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,62 +2466,81 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296431</v>
+        <v>125305277</v>
       </c>
       <c r="B18" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589354</v>
+        <v>589383</v>
       </c>
       <c r="R18" t="n">
-        <v>6931848</v>
+        <v>6931790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,19 +2570,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,50 +2604,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125299331</v>
+        <v>125296431</v>
       </c>
       <c r="B19" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589048</v>
+        <v>589354</v>
       </c>
       <c r="R19" t="n">
-        <v>6931702</v>
+        <v>6931848</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2754,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,27 +2699,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125296103</v>
+        <v>125295434</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2797,39 +2722,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589391</v>
+        <v>589353</v>
       </c>
       <c r="R20" t="n">
-        <v>6931808</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,12 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,15 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125294978</v>
+        <v>125299895</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,34 +2829,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589387</v>
+        <v>588936</v>
       </c>
       <c r="R21" t="n">
-        <v>6931823</v>
+        <v>6931778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2978,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2988,7 +2903,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,67 +2923,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125296528</v>
+        <v>125294462</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589358</v>
+        <v>589418</v>
       </c>
       <c r="R22" t="n">
-        <v>6931874</v>
+        <v>6931797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3095,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3105,12 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,15 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125300799</v>
+        <v>125298949</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3153,39 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589008</v>
+        <v>589168</v>
       </c>
       <c r="R23" t="n">
-        <v>6931783</v>
+        <v>6931676</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,12 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,6 +3146,1461 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125875003</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>588981</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6931726</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125868133</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>589362</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6931820</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125876618</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>588850</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6931691</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125873916</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>589123</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6931688</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125877168</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91170</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>112</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>589015</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6931702</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125875029</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588962</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6931754</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjäder av järpe</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125868029</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98244</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>589362</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6931820</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125873741</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>589223</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6931676</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125875088</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>588945</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6931766</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125874977</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>588973</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6931744</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125875367</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>588882</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6931753</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125875151</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NB Bastumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>588943</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6931767</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125867683</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56227</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Palmastjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>589391</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6931834</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1022,32 +1022,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296528</v>
+        <v>125296103</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589358</v>
+        <v>589391</v>
       </c>
       <c r="R5" t="n">
-        <v>6931874</v>
+        <v>6931808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fjäder ( dun )</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,32 +1139,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296103</v>
+        <v>125296528</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589391</v>
+        <v>589358</v>
       </c>
       <c r="R6" t="n">
-        <v>6931808</v>
+        <v>6931874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1819,7 +1819,7 @@
         <v>125299553</v>
       </c>
       <c r="B12" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125301135</v>
+        <v>125299044</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1954,7 +1954,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589154</v>
+        <v>589157</v>
       </c>
       <c r="R13" t="n">
-        <v>6931760</v>
+        <v>6931653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125299044</v>
+        <v>125301135</v>
       </c>
       <c r="B15" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,16 +2153,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2178,7 +2173,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2187,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589157</v>
+        <v>589154</v>
       </c>
       <c r="R15" t="n">
-        <v>6931653</v>
+        <v>6931760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2227,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,7 +2374,7 @@
         <v>125298269</v>
       </c>
       <c r="B17" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,69 +2478,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125305277</v>
+        <v>125296431</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>80098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589383</v>
+        <v>589354</v>
       </c>
       <c r="R18" t="n">
-        <v>6931790</v>
+        <v>6931848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,14 +2546,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,32 +2585,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125296431</v>
+        <v>125295434</v>
       </c>
       <c r="B19" t="n">
-        <v>80098</v>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589354</v>
+        <v>589353</v>
       </c>
       <c r="R19" t="n">
-        <v>6931848</v>
+        <v>6931796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125295434</v>
+        <v>125299895</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,34 +2703,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589353</v>
+        <v>588936</v>
       </c>
       <c r="R20" t="n">
-        <v>6931796</v>
+        <v>6931778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2777,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,19 +2797,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125299895</v>
+        <v>125305277</v>
       </c>
       <c r="B21" t="n">
         <v>57651</v>
@@ -2846,22 +2837,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588936</v>
+        <v>589383</v>
       </c>
       <c r="R21" t="n">
-        <v>6931778</v>
+        <v>6931790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,24 +2901,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,12 +2923,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
         <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>91177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R27" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>91170</v>
+        <v>80070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R28" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
+        <v>98251</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1022,32 +1022,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296103</v>
+        <v>125296528</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589391</v>
+        <v>589358</v>
       </c>
       <c r="R5" t="n">
-        <v>6931808</v>
+        <v>6931874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,32 +1139,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296528</v>
+        <v>125296103</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589358</v>
+        <v>589391</v>
       </c>
       <c r="R6" t="n">
-        <v>6931874</v>
+        <v>6931808</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjäder ( dun )</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3264,7 +3264,7 @@
         <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B27" t="n">
-        <v>91177</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R27" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>91178</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R28" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98251</v>
+        <v>98252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>125875367</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>125294642</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,32 +1022,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296528</v>
+        <v>125296103</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589358</v>
+        <v>589391</v>
       </c>
       <c r="R5" t="n">
-        <v>6931874</v>
+        <v>6931808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fjäder ( dun )</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,32 +1139,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296103</v>
+        <v>125296528</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589391</v>
+        <v>589358</v>
       </c>
       <c r="R6" t="n">
-        <v>6931808</v>
+        <v>6931874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,7 +1376,7 @@
         <v>125294611</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>125294978</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125299553</v>
       </c>
       <c r="B12" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299044</v>
+        <v>125299331</v>
       </c>
       <c r="B13" t="n">
-        <v>56834</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,39 +1934,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589157</v>
+        <v>589048</v>
       </c>
       <c r="R13" t="n">
-        <v>6931653</v>
+        <v>6931702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125299331</v>
+        <v>125299044</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>56834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,34 +2041,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589048</v>
+        <v>589157</v>
       </c>
       <c r="R14" t="n">
-        <v>6931702</v>
+        <v>6931653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2374,7 +2374,7 @@
         <v>125298269</v>
       </c>
       <c r="B17" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>125296431</v>
       </c>
       <c r="B18" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>125295434</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>125294462</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125298949</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,50 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>98355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,57 +3244,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B25" t="n">
-        <v>98353</v>
+        <v>57811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>91178</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R27" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>91178</v>
+        <v>80071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R28" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98252</v>
+        <v>98254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299331</v>
+        <v>125299044</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>56834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,34 +1934,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589048</v>
+        <v>589157</v>
       </c>
       <c r="R13" t="n">
-        <v>6931702</v>
+        <v>6931653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125299044</v>
+        <v>125301135</v>
       </c>
       <c r="B14" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,16 +2046,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2061,7 +2066,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2070,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589157</v>
+        <v>589154</v>
       </c>
       <c r="R14" t="n">
-        <v>6931653</v>
+        <v>6931760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2120,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125301135</v>
+        <v>125299331</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,39 +2163,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589154</v>
+        <v>589048</v>
       </c>
       <c r="R15" t="n">
-        <v>6931760</v>
+        <v>6931702</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,45 +3149,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R24" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,62 +3249,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R25" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B27" t="n">
-        <v>91178</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R27" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>91182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R28" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98254</v>
+        <v>98258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>125875367</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,50 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,57 +3244,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>57811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,45 +3149,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R24" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,62 +3249,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>57811</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R25" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>91182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R27" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>91182</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R28" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,50 +3693,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125875029</v>
+        <v>125868029</v>
       </c>
       <c r="B29" t="n">
-        <v>56834</v>
+        <v>98259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588962</v>
+        <v>589362</v>
       </c>
       <c r="R29" t="n">
-        <v>6931754</v>
+        <v>6931820</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3768,7 +3763,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3778,12 +3773,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjäder av järpe</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,45 +3800,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125868029</v>
+        <v>125875029</v>
       </c>
       <c r="B30" t="n">
-        <v>98258</v>
+        <v>56834</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223597</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589362</v>
+        <v>588962</v>
       </c>
       <c r="R30" t="n">
-        <v>6931820</v>
+        <v>6931754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3880,7 +3875,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3885,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fjäder av järpe</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3152,7 +3152,7 @@
         <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125868029</v>
       </c>
       <c r="B29" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125875029</v>
       </c>
       <c r="B30" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>125873741</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>125875088</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>125874977</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>125875367</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125875151</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>125867683</v>
       </c>
       <c r="B36" t="n">
-        <v>56227</v>
+        <v>56228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,50 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>57812</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,57 +3244,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B25" t="n">
-        <v>98362</v>
+        <v>57812</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3693,45 +3693,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125868029</v>
+        <v>125875029</v>
       </c>
       <c r="B29" t="n">
-        <v>98261</v>
+        <v>56835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589362</v>
+        <v>588962</v>
       </c>
       <c r="R29" t="n">
-        <v>6931820</v>
+        <v>6931754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3763,7 +3768,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3773,7 +3778,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjäder av järpe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,50 +3810,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125875029</v>
+        <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>56835</v>
+        <v>98261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>223597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588962</v>
+        <v>589362</v>
       </c>
       <c r="R30" t="n">
-        <v>6931754</v>
+        <v>6931820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,7 +3880,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3885,12 +3890,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fjäder av järpe</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3152,7 +3152,7 @@
         <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3152,7 +3152,7 @@
         <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>91186</v>
+        <v>91188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,45 +3149,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>57812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R24" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,62 +3249,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>57812</v>
+        <v>98366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R25" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B27" t="n">
-        <v>91188</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R27" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>91188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R28" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3152,7 +3152,7 @@
         <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>125873916</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>125877168</v>
       </c>
       <c r="B28" t="n">
-        <v>91188</v>
+        <v>91192</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125875029</v>
       </c>
       <c r="B29" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>125873741</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125875088</v>
+        <v>125874977</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588945</v>
+        <v>588973</v>
       </c>
       <c r="R32" t="n">
-        <v>6931766</v>
+        <v>6931744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4151,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125874977</v>
+        <v>125875088</v>
       </c>
       <c r="B33" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588973</v>
+        <v>588945</v>
       </c>
       <c r="R33" t="n">
-        <v>6931744</v>
+        <v>6931766</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4271,7 +4271,7 @@
         <v>125875367</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125875151</v>
       </c>
       <c r="B35" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>125867683</v>
       </c>
       <c r="B36" t="n">
-        <v>56228</v>
+        <v>56232</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3264,7 +3264,7 @@
         <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125874977</v>
+        <v>125875088</v>
       </c>
       <c r="B32" t="n">
         <v>57656</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588973</v>
+        <v>588945</v>
       </c>
       <c r="R32" t="n">
-        <v>6931744</v>
+        <v>6931766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4151,7 +4151,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125875088</v>
+        <v>125874977</v>
       </c>
       <c r="B33" t="n">
         <v>57656</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588945</v>
+        <v>588973</v>
       </c>
       <c r="R33" t="n">
-        <v>6931766</v>
+        <v>6931744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125873916</v>
+        <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>91192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589123</v>
+        <v>589015</v>
       </c>
       <c r="R27" t="n">
-        <v>6931688</v>
+        <v>6931702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877168</v>
+        <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>91192</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589015</v>
+        <v>589123</v>
       </c>
       <c r="R28" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,50 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,57 +3244,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>57816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,45 +3149,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R24" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,62 +3249,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>57816</v>
+        <v>98382</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R25" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>125876618</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>125877168</v>
       </c>
       <c r="B27" t="n">
-        <v>91192</v>
+        <v>91195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>125873916</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125875029</v>
       </c>
       <c r="B29" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125868029</v>
       </c>
       <c r="B30" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>125873741</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>125875088</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>125874977</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>125875367</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125875151</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>125867683</v>
       </c>
       <c r="B36" t="n">
-        <v>56232</v>
+        <v>56233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,50 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,57 +3244,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B25" t="n">
-        <v>98382</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -3149,45 +3149,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125868133</v>
+        <v>125875003</v>
       </c>
       <c r="B24" t="n">
-        <v>98382</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589362</v>
+        <v>588981</v>
       </c>
       <c r="R24" t="n">
-        <v>6931820</v>
+        <v>6931726</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,62 +3249,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125875003</v>
+        <v>125868133</v>
       </c>
       <c r="B25" t="n">
-        <v>57817</v>
+        <v>98382</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588981</v>
+        <v>589362</v>
       </c>
       <c r="R25" t="n">
-        <v>6931726</v>
+        <v>6931820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,12 +3356,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>125295350</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>125298647</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125300799</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>125296103</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>125300846</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>125300204</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>125301135</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>125299895</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>125873741</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>125875088</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>125874977</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125875151</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125300799</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>125296103</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>125300846</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>125300204</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>125301135</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>125299895</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>125873741</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>125875088</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>125874977</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125875151</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4602,6 +4602,648 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132783571</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>589147</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6931687</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132783587</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>589210</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6931708</v>
+      </c>
+      <c r="S38" t="n">
+        <v>7</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132783574</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>589142</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6931747</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132783572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>589142</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6931743</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132783573</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>589141</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6931743</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132783570</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>589297</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6931737</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -5032,32 +5032,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132783573</v>
+        <v>132783570</v>
       </c>
       <c r="B41" t="n">
-        <v>91923</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5067,13 +5067,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589141</v>
+        <v>589297</v>
       </c>
       <c r="R41" t="n">
-        <v>6931743</v>
+        <v>6931737</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5139,32 +5139,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132783570</v>
+        <v>132783573</v>
       </c>
       <c r="B42" t="n">
-        <v>80461</v>
+        <v>91923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5174,13 +5174,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589297</v>
+        <v>589141</v>
       </c>
       <c r="R42" t="n">
-        <v>6931737</v>
+        <v>6931743</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -4607,7 +4607,7 @@
         <v>132783571</v>
       </c>
       <c r="B37" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>132783587</v>
       </c>
       <c r="B38" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>132783574</v>
       </c>
       <c r="B39" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>132783572</v>
       </c>
       <c r="B40" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>132783570</v>
       </c>
       <c r="B41" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>132783573</v>
       </c>
       <c r="B42" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -5142,7 +5142,7 @@
         <v>132783573</v>
       </c>
       <c r="B42" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124845031</v>
+        <v>125877168</v>
       </c>
       <c r="B2" t="n">
-        <v>56939</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pallamstjärn, Västanbäck,  Stöde, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589476</v>
+        <v>589015</v>
       </c>
       <c r="R2" t="n">
-        <v>6931683</v>
+        <v>6931702</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Löfqvist</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Löfqvist</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125300799</v>
+        <v>132783572</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589008</v>
+        <v>589142</v>
       </c>
       <c r="R3" t="n">
-        <v>6931783</v>
+        <v>6931743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125294642</v>
+        <v>132783574</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589418</v>
+        <v>589142</v>
       </c>
       <c r="R4" t="n">
-        <v>6931797</v>
+        <v>6931747</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,65 +984,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125296103</v>
+        <v>132783573</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589391</v>
+        <v>589141</v>
       </c>
       <c r="R5" t="n">
-        <v>6931808</v>
+        <v>6931743</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,27 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,62 +1091,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125296528</v>
+        <v>125294611</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589358</v>
+        <v>589420</v>
       </c>
       <c r="R6" t="n">
-        <v>6931874</v>
+        <v>6931807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fjäder ( dun )</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125300846</v>
+        <v>125294642</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589033</v>
+        <v>589418</v>
       </c>
       <c r="R7" t="n">
-        <v>6931798</v>
+        <v>6931797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,26 +1305,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125294611</v>
+        <v>125296711</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1408,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589420</v>
+        <v>589389</v>
       </c>
       <c r="R8" t="n">
-        <v>6931807</v>
+        <v>6931877</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125300204</v>
+        <v>125298949</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588968</v>
+        <v>589168</v>
       </c>
       <c r="R9" t="n">
-        <v>6931778</v>
+        <v>6931676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125294978</v>
+        <v>132783571</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>80382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589387</v>
+        <v>589147</v>
       </c>
       <c r="R10" t="n">
-        <v>6931823</v>
+        <v>6931687</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,22 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125295350</v>
+        <v>125294462</v>
       </c>
       <c r="B11" t="n">
-        <v>57681</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589353</v>
+        <v>589418</v>
       </c>
       <c r="R11" t="n">
-        <v>6931796</v>
+        <v>6931797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,45 +1745,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125299553</v>
+        <v>125294978</v>
       </c>
       <c r="B12" t="n">
-        <v>100516</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589043</v>
+        <v>589387</v>
       </c>
       <c r="R12" t="n">
-        <v>6931742</v>
+        <v>6931823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,22 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125299044</v>
+        <v>125295434</v>
       </c>
       <c r="B13" t="n">
-        <v>56834</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,39 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589157</v>
+        <v>589353</v>
       </c>
       <c r="R13" t="n">
-        <v>6931653</v>
+        <v>6931796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,22 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125301135</v>
+        <v>125299331</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,39 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589154</v>
+        <v>589048</v>
       </c>
       <c r="R14" t="n">
-        <v>6931760</v>
+        <v>6931702</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,12 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125299331</v>
+        <v>125873916</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589048</v>
+        <v>589123</v>
       </c>
       <c r="R15" t="n">
-        <v>6931702</v>
+        <v>6931688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,22 +2131,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,22 +2161,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125298647</v>
+        <v>125875367</v>
       </c>
       <c r="B16" t="n">
-        <v>57681</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,39 +2184,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589287</v>
+        <v>588882</v>
       </c>
       <c r="R16" t="n">
-        <v>6931646</v>
+        <v>6931753</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,22 +2268,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125298269</v>
+        <v>125296431</v>
       </c>
       <c r="B17" t="n">
-        <v>97212</v>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,34 +2291,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589340</v>
+        <v>589354</v>
       </c>
       <c r="R17" t="n">
-        <v>6931710</v>
+        <v>6931848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,22 +2375,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125296431</v>
+        <v>132783570</v>
       </c>
       <c r="B18" t="n">
-        <v>80099</v>
+        <v>80493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589354</v>
+        <v>589297</v>
       </c>
       <c r="R18" t="n">
-        <v>6931848</v>
+        <v>6931737</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2543,22 +2452,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,60 +2482,76 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125295434</v>
+        <v>124845031</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>57247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100038</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Pallamstjärn, Västanbäck,  Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589353</v>
+        <v>589476</v>
       </c>
       <c r="R19" t="n">
-        <v>6931796</v>
+        <v>6931683</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2650,22 +2575,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,39 +2605,39 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Thomas Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Thomas Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125299895</v>
+        <v>125295350</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2728,14 +2653,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588936</v>
+        <v>589353</v>
       </c>
       <c r="R20" t="n">
-        <v>6931778</v>
+        <v>6931796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,12 +2702,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färskt och äldre</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,39 +2717,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125305277</v>
+        <v>125298647</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2837,41 +2757,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589383</v>
+        <v>589287</v>
       </c>
       <c r="R21" t="n">
-        <v>6931790</v>
+        <v>6931646</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,14 +2802,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,22 +2829,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294462</v>
+        <v>125296103</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,34 +2852,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589418</v>
+        <v>589391</v>
       </c>
       <c r="R22" t="n">
-        <v>6931797</v>
+        <v>6931808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2916,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +2926,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125298949</v>
+        <v>125299895</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,34 +2969,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kångeråbäcken, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589168</v>
+        <v>588936</v>
       </c>
       <c r="R23" t="n">
-        <v>6931676</v>
+        <v>6931778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3033,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3043,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färskt och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125875003</v>
+        <v>125300204</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,27 +3086,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3189,10 +3115,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588981</v>
+        <v>588968</v>
       </c>
       <c r="R24" t="n">
-        <v>6931726</v>
+        <v>6931778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,22 +3145,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,45 +3192,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125868133</v>
+        <v>125300799</v>
       </c>
       <c r="B25" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589362</v>
+        <v>589008</v>
       </c>
       <c r="R25" t="n">
-        <v>6931820</v>
+        <v>6931783</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,22 +3262,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,49 +3297,50 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876618</v>
+        <v>125300846</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3407,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588850</v>
+        <v>589033</v>
       </c>
       <c r="R26" t="n">
-        <v>6931691</v>
+        <v>6931798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3437,22 +3379,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,10 +3426,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877168</v>
+        <v>125301135</v>
       </c>
       <c r="B27" t="n">
-        <v>91195</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,34 +3437,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589015</v>
+        <v>589154</v>
       </c>
       <c r="R27" t="n">
-        <v>6931702</v>
+        <v>6931760</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,22 +3496,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,22 +3531,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125873916</v>
+        <v>125305277</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,34 +3554,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>Palmastjärnen, NB Bastumyran, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589123</v>
+        <v>589383</v>
       </c>
       <c r="R28" t="n">
-        <v>6931688</v>
+        <v>6931790</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,22 +3632,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosök, Tretåig hackspett hona, mellan video inspelningarna kan en annan Tretåig hackspett höras trumma en bit bort.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125875029</v>
+        <v>125873741</v>
       </c>
       <c r="B29" t="n">
-        <v>56840</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,16 +3680,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3733,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588962</v>
+        <v>589223</v>
       </c>
       <c r="R29" t="n">
-        <v>6931754</v>
+        <v>6931676</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3768,7 +3744,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3778,12 +3754,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Fjäder av järpe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3798,57 +3774,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125868029</v>
+        <v>125874977</v>
       </c>
       <c r="B30" t="n">
-        <v>98281</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589362</v>
+        <v>588973</v>
       </c>
       <c r="R30" t="n">
-        <v>6931820</v>
+        <v>6931744</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3880,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3871,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3905,22 +3891,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125873741</v>
+        <v>125875088</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3957,10 +3943,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589223</v>
+        <v>588945</v>
       </c>
       <c r="R31" t="n">
-        <v>6931676</v>
+        <v>6931766</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3992,7 +3978,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4002,7 +3988,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4034,10 +4020,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125875088</v>
+        <v>125875151</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588945</v>
+        <v>588943</v>
       </c>
       <c r="R32" t="n">
-        <v>6931766</v>
+        <v>6931767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4095,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,12 +4105,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,44 +4125,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125874977</v>
+        <v>125296528</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,14 +4173,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588973</v>
+        <v>589358</v>
       </c>
       <c r="R33" t="n">
-        <v>6931744</v>
+        <v>6931874</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4221,27 +4207,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjäder ( dun )</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,57 +4242,62 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125875367</v>
+        <v>125299044</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>57132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>NB Bastumyran, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588882</v>
+        <v>589157</v>
       </c>
       <c r="R34" t="n">
-        <v>6931753</v>
+        <v>6931653</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4333,22 +4324,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,39 +4354,39 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125875151</v>
+        <v>125875029</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4415,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588943</v>
+        <v>588962</v>
       </c>
       <c r="R35" t="n">
-        <v>6931767</v>
+        <v>6931754</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4450,7 +4441,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,12 +4451,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Fjäder av järpe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125867683</v>
+        <v>125875003</v>
       </c>
       <c r="B36" t="n">
-        <v>56233</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,39 +4494,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Palmastjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589391</v>
+        <v>588981</v>
       </c>
       <c r="R36" t="n">
-        <v>6931834</v>
+        <v>6931726</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4577,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4592,60 +4583,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132783571</v>
+        <v>125867683</v>
       </c>
       <c r="B37" t="n">
-        <v>80342</v>
+        <v>56522</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>206004</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Palmastjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589147</v>
+        <v>589391</v>
       </c>
       <c r="R37" t="n">
-        <v>6931687</v>
+        <v>6931834</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4669,22 +4665,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,60 +4695,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132783587</v>
+        <v>125876618</v>
       </c>
       <c r="B38" t="n">
-        <v>80398</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589210</v>
+        <v>588850</v>
       </c>
       <c r="R38" t="n">
-        <v>6931708</v>
+        <v>6931691</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4776,22 +4776,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,48 +4818,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132783574</v>
+        <v>125298269</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>97983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589142</v>
+        <v>589340</v>
       </c>
       <c r="R39" t="n">
-        <v>6931747</v>
+        <v>6931710</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4925,32 +4925,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132783572</v>
+        <v>125868133</v>
       </c>
       <c r="B40" t="n">
-        <v>92217</v>
+        <v>99140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589142</v>
+        <v>589362</v>
       </c>
       <c r="R40" t="n">
-        <v>6931743</v>
+        <v>6931820</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4990,22 +4990,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,22 +5020,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132783570</v>
+        <v>125299553</v>
       </c>
       <c r="B41" t="n">
-        <v>80467</v>
+        <v>101326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5043,37 +5043,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>NB Bastumyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589297</v>
+        <v>589043</v>
       </c>
       <c r="R41" t="n">
-        <v>6931737</v>
+        <v>6931742</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,22 +5097,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5139,48 +5139,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132783573</v>
+        <v>125301027</v>
       </c>
       <c r="B42" t="n">
-        <v>91934</v>
+        <v>101326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Palamstjärnen, Mpd</t>
+          <t>Kångeråbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589141</v>
+        <v>589108</v>
       </c>
       <c r="R42" t="n">
-        <v>6931743</v>
+        <v>6931778</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5204,22 +5204,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5243,6 +5243,113 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132783587</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>589210</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6931708</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8732-2025 artfynd.xlsx
+++ b/artfynd/A 8732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783574</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294611</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783571</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294462</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294978</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125295434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299331</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873916</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875367</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783570</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2614,6 +2704,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124845031</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2726,6 +2821,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125295350</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2838,6 +2938,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298647</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296103</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299895</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3189,6 +3304,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300204</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300799</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3423,6 +3548,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300846</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3540,6 +3670,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301135</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3666,6 +3801,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125305277</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3783,6 +3923,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873741</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3900,6 +4045,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125874977</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4017,6 +4167,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875088</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4251,6 +4411,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125296528</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4363,6 +4528,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299044</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4480,6 +4650,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875029</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4592,6 +4767,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875003</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4704,6 +4884,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125867683</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4815,6 +5000,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125876618</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4922,6 +5112,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298269</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5029,6 +5224,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125868133</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5136,6 +5336,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299553</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5243,6 +5448,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301027</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5350,8 +5560,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783587</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>